--- a/Registration.xlsx
+++ b/Registration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsamak\Workspace\AutoDRIVE-RoboRacer-Sim-Racing-Participation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407E20E1-20F5-488C-AC3B-0F7A6B228563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568BC0AB-9A73-47D1-BC33-70BCC68276EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="5" xr2:uid="{5D9342A3-8B90-4963-824C-8C358DE1DB7F}"/>
   </bookViews>
@@ -3922,7 +3922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3944,9 +3944,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6206,85 +6203,37 @@
     </row>
   </sheetData>
   <mergeCells count="124">
-    <mergeCell ref="E159:E161"/>
-    <mergeCell ref="E135:E137"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="E142:E148"/>
-    <mergeCell ref="E149:E152"/>
-    <mergeCell ref="E154:E158"/>
-    <mergeCell ref="E111:E116"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E122:E123"/>
-    <mergeCell ref="E124:E131"/>
-    <mergeCell ref="E132:E134"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="E99:E102"/>
-    <mergeCell ref="E103:E105"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="E71:E76"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="E84:E89"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="E35:E46"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="E59:E65"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="E6:E14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="B35:B46"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="B6:B14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="B59:B65"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="A103:A105"/>
-    <mergeCell ref="B103:B105"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="A84:A89"/>
-    <mergeCell ref="B84:B89"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="A124:A131"/>
-    <mergeCell ref="B124:B131"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="A111:A116"/>
-    <mergeCell ref="B111:B116"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D6:D14"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="D71:D76"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="D59:D65"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="D35:D46"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D103:D105"/>
+    <mergeCell ref="D99:D102"/>
+    <mergeCell ref="D111:D116"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="D117:D118"/>
+    <mergeCell ref="D95:D97"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="D84:D89"/>
+    <mergeCell ref="D154:D158"/>
+    <mergeCell ref="D159:D161"/>
+    <mergeCell ref="D124:D131"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="D135:D137"/>
+    <mergeCell ref="D132:D134"/>
+    <mergeCell ref="D149:D152"/>
+    <mergeCell ref="D142:D148"/>
     <mergeCell ref="A142:A148"/>
     <mergeCell ref="B142:B148"/>
     <mergeCell ref="A159:A161"/>
@@ -6299,37 +6248,85 @@
     <mergeCell ref="B135:B137"/>
     <mergeCell ref="A138:A141"/>
     <mergeCell ref="B138:B141"/>
-    <mergeCell ref="D154:D158"/>
-    <mergeCell ref="D159:D161"/>
-    <mergeCell ref="D124:D131"/>
-    <mergeCell ref="D122:D123"/>
-    <mergeCell ref="D138:D141"/>
-    <mergeCell ref="D135:D137"/>
-    <mergeCell ref="D132:D134"/>
-    <mergeCell ref="D149:D152"/>
-    <mergeCell ref="D142:D148"/>
-    <mergeCell ref="D103:D105"/>
-    <mergeCell ref="D99:D102"/>
-    <mergeCell ref="D111:D116"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="D117:D118"/>
-    <mergeCell ref="D95:D97"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="D84:D89"/>
-    <mergeCell ref="D27:D31"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D6:D14"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="D71:D76"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="D59:D65"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="D35:D46"/>
-    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="A124:A131"/>
+    <mergeCell ref="B124:B131"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="A111:A116"/>
+    <mergeCell ref="B111:B116"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="A84:A89"/>
+    <mergeCell ref="B84:B89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="A59:A65"/>
+    <mergeCell ref="B59:B65"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="B35:B46"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="B6:B14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="E35:E46"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E59:E65"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="E6:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E95:E97"/>
+    <mergeCell ref="E99:E102"/>
+    <mergeCell ref="E103:E105"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="E71:E76"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="E84:E89"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="E159:E161"/>
+    <mergeCell ref="E135:E137"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E142:E148"/>
+    <mergeCell ref="E149:E152"/>
+    <mergeCell ref="E154:E158"/>
+    <mergeCell ref="E111:E116"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="E122:E123"/>
+    <mergeCell ref="E124:E131"/>
+    <mergeCell ref="E132:E134"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -8301,44 +8298,88 @@
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="E166:E169"/>
-    <mergeCell ref="E170:E171"/>
-    <mergeCell ref="E102:E111"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="E117:E122"/>
-    <mergeCell ref="E123:E129"/>
-    <mergeCell ref="E130:E141"/>
-    <mergeCell ref="E142:E145"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="E152:E156"/>
-    <mergeCell ref="E75:E78"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="E157:E159"/>
-    <mergeCell ref="E160:E164"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E62:E64"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="B8:B15"/>
-    <mergeCell ref="D8:D15"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="E8:E15"/>
-    <mergeCell ref="E16:E19"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="D71:D73"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="B46:B51"/>
+    <mergeCell ref="D46:D51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A152:A156"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="A130:A141"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A102:A111"/>
+    <mergeCell ref="A117:A122"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="A160:A164"/>
+    <mergeCell ref="B160:B164"/>
+    <mergeCell ref="D160:D164"/>
+    <mergeCell ref="A157:A159"/>
+    <mergeCell ref="B157:B159"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="D112:D116"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="D95:D97"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="D86:D91"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B152:B156"/>
+    <mergeCell ref="D152:D156"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="D117:D122"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="B102:B111"/>
+    <mergeCell ref="D102:D111"/>
+    <mergeCell ref="B123:B129"/>
+    <mergeCell ref="D123:D129"/>
+    <mergeCell ref="B130:B141"/>
+    <mergeCell ref="D130:D141"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D146:D149"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:D3"/>
@@ -8363,88 +8404,44 @@
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="D16:D19"/>
     <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B152:B156"/>
-    <mergeCell ref="D152:D156"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="D117:D122"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="B102:B111"/>
-    <mergeCell ref="D102:D111"/>
-    <mergeCell ref="B123:B129"/>
-    <mergeCell ref="D123:D129"/>
-    <mergeCell ref="B130:B141"/>
-    <mergeCell ref="D130:D141"/>
-    <mergeCell ref="B142:B145"/>
-    <mergeCell ref="D142:D145"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="D95:D97"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B86:B91"/>
-    <mergeCell ref="D86:D91"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="D166:D169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="A160:A164"/>
-    <mergeCell ref="B160:B164"/>
-    <mergeCell ref="D160:D164"/>
-    <mergeCell ref="A157:A159"/>
-    <mergeCell ref="B157:B159"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="A152:A156"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A166:A169"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="A130:A141"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A142:A145"/>
-    <mergeCell ref="A146:A149"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="A86:A91"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A102:A111"/>
-    <mergeCell ref="A117:A122"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="D71:D73"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="B46:B51"/>
-    <mergeCell ref="D46:D51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="E8:E15"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E62:E64"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="B8:B15"/>
+    <mergeCell ref="D8:D15"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="E75:E78"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="E95:E97"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="E157:E159"/>
+    <mergeCell ref="E160:E164"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="E170:E171"/>
+    <mergeCell ref="E102:E111"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="E117:E122"/>
+    <mergeCell ref="E123:E129"/>
+    <mergeCell ref="E130:E141"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="E152:E156"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -10279,90 +10276,29 @@
     </row>
   </sheetData>
   <mergeCells count="132">
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="D145:D147"/>
-    <mergeCell ref="E145:E147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="B149:B150"/>
-    <mergeCell ref="D149:D150"/>
-    <mergeCell ref="E149:E150"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="E131:E133"/>
-    <mergeCell ref="A135:A138"/>
-    <mergeCell ref="B135:B138"/>
-    <mergeCell ref="D135:D138"/>
-    <mergeCell ref="E135:E138"/>
-    <mergeCell ref="A139:A141"/>
-    <mergeCell ref="B139:B141"/>
-    <mergeCell ref="D139:D141"/>
-    <mergeCell ref="E139:E141"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="A118:A127"/>
-    <mergeCell ref="B118:B127"/>
-    <mergeCell ref="D118:D127"/>
-    <mergeCell ref="E118:E127"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="D81:D85"/>
-    <mergeCell ref="E81:E85"/>
-    <mergeCell ref="E87:E89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="B60:B64"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="E42:E46"/>
-    <mergeCell ref="E73:E75"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="E65:E71"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="D129:D130"/>
+    <mergeCell ref="E129:E130"/>
+    <mergeCell ref="A87:A89"/>
+    <mergeCell ref="B87:B89"/>
+    <mergeCell ref="D87:D89"/>
+    <mergeCell ref="A92:A97"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="D92:D97"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="A99:A109"/>
+    <mergeCell ref="B99:B109"/>
+    <mergeCell ref="D99:D109"/>
+    <mergeCell ref="E99:E109"/>
+    <mergeCell ref="A76:A80"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="E76:E80"/>
+    <mergeCell ref="A65:A71"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="D65:D71"/>
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="E29:E31"/>
     <mergeCell ref="A20:A22"/>
@@ -10387,30 +10323,91 @@
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="B1:B4"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="E65:E71"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
-    <mergeCell ref="E48:E50"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="D129:D130"/>
-    <mergeCell ref="E129:E130"/>
-    <mergeCell ref="A87:A89"/>
-    <mergeCell ref="B87:B89"/>
-    <mergeCell ref="D87:D89"/>
-    <mergeCell ref="A92:A97"/>
-    <mergeCell ref="B92:B97"/>
-    <mergeCell ref="D92:D97"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="A99:A109"/>
-    <mergeCell ref="B99:B109"/>
-    <mergeCell ref="D99:D109"/>
-    <mergeCell ref="E99:E109"/>
-    <mergeCell ref="A76:A80"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="E76:E80"/>
-    <mergeCell ref="A65:A71"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="D65:D71"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="D81:D85"/>
+    <mergeCell ref="E81:E85"/>
+    <mergeCell ref="E87:E89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="A118:A127"/>
+    <mergeCell ref="B118:B127"/>
+    <mergeCell ref="D118:D127"/>
+    <mergeCell ref="E118:E127"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="D145:D147"/>
+    <mergeCell ref="E145:E147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="D149:D150"/>
+    <mergeCell ref="E149:E150"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="E131:E133"/>
+    <mergeCell ref="A135:A138"/>
+    <mergeCell ref="B135:B138"/>
+    <mergeCell ref="D135:D138"/>
+    <mergeCell ref="E135:E138"/>
+    <mergeCell ref="A139:A141"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="D139:D141"/>
+    <mergeCell ref="E139:E141"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -12209,31 +12206,57 @@
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="D32:D35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="B83:B89"/>
-    <mergeCell ref="D83:D89"/>
-    <mergeCell ref="E83:E89"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="D62:D67"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="A69:A72"/>
-    <mergeCell ref="B69:B72"/>
-    <mergeCell ref="D69:D72"/>
-    <mergeCell ref="E69:E72"/>
-    <mergeCell ref="A73:A82"/>
-    <mergeCell ref="B73:B82"/>
-    <mergeCell ref="D73:D82"/>
-    <mergeCell ref="E73:E82"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="A96:A100"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="A83:A89"/>
+    <mergeCell ref="A154:A156"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="D154:D156"/>
+    <mergeCell ref="E154:E156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="D90:D95"/>
+    <mergeCell ref="E90:E95"/>
+    <mergeCell ref="B96:B100"/>
+    <mergeCell ref="D96:D100"/>
+    <mergeCell ref="E96:E100"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="D49:D54"/>
+    <mergeCell ref="E49:E54"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="D42:D47"/>
+    <mergeCell ref="E42:E47"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="A15:A24"/>
+    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="D15:D24"/>
+    <mergeCell ref="E15:E24"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="E28:E31"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="E9:E13"/>
     <mergeCell ref="A129:A151"/>
     <mergeCell ref="B129:B151"/>
     <mergeCell ref="D129:D151"/>
@@ -12250,57 +12273,31 @@
     <mergeCell ref="B126:B128"/>
     <mergeCell ref="D126:D128"/>
     <mergeCell ref="E126:E128"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="A15:A24"/>
-    <mergeCell ref="B15:B24"/>
-    <mergeCell ref="D15:D24"/>
-    <mergeCell ref="E15:E24"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="D42:D47"/>
-    <mergeCell ref="E42:E47"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="D49:D54"/>
-    <mergeCell ref="E49:E54"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="D57:D61"/>
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="D90:D95"/>
-    <mergeCell ref="E90:E95"/>
-    <mergeCell ref="B96:B100"/>
-    <mergeCell ref="D96:D100"/>
-    <mergeCell ref="E96:E100"/>
-    <mergeCell ref="B90:B95"/>
-    <mergeCell ref="A154:A156"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="D154:D156"/>
-    <mergeCell ref="E154:E156"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A90:A95"/>
-    <mergeCell ref="A96:A100"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="A83:A89"/>
+    <mergeCell ref="B83:B89"/>
+    <mergeCell ref="D83:D89"/>
+    <mergeCell ref="E83:E89"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="D62:D67"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="A69:A72"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="D69:D72"/>
+    <mergeCell ref="E69:E72"/>
+    <mergeCell ref="A73:A82"/>
+    <mergeCell ref="B73:B82"/>
+    <mergeCell ref="D73:D82"/>
+    <mergeCell ref="E73:E82"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="E32:E35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14713,102 +14710,30 @@
     </row>
   </sheetData>
   <mergeCells count="144">
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="D182:D183"/>
-    <mergeCell ref="E182:E183"/>
-    <mergeCell ref="A185:A191"/>
-    <mergeCell ref="B185:B191"/>
-    <mergeCell ref="D185:D191"/>
-    <mergeCell ref="E185:E191"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="D176:D177"/>
-    <mergeCell ref="E176:E177"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="D178:D181"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="A168:A170"/>
-    <mergeCell ref="B168:B170"/>
-    <mergeCell ref="D168:D170"/>
-    <mergeCell ref="E168:E170"/>
-    <mergeCell ref="A171:A175"/>
-    <mergeCell ref="B171:B175"/>
-    <mergeCell ref="D171:D175"/>
-    <mergeCell ref="E171:E175"/>
-    <mergeCell ref="A154:A161"/>
-    <mergeCell ref="B154:B161"/>
-    <mergeCell ref="D154:D161"/>
-    <mergeCell ref="E154:E161"/>
-    <mergeCell ref="A163:A165"/>
-    <mergeCell ref="B163:B165"/>
-    <mergeCell ref="D163:D165"/>
-    <mergeCell ref="E163:E165"/>
-    <mergeCell ref="A145:A149"/>
-    <mergeCell ref="B145:B149"/>
-    <mergeCell ref="D145:D149"/>
-    <mergeCell ref="E145:E149"/>
-    <mergeCell ref="A151:A153"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="D151:D153"/>
-    <mergeCell ref="E151:E153"/>
-    <mergeCell ref="D139:D141"/>
-    <mergeCell ref="E139:E141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="D125:D127"/>
-    <mergeCell ref="E125:E127"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="E132:E133"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="E111:E112"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="B115:B123"/>
-    <mergeCell ref="D115:D123"/>
-    <mergeCell ref="E115:E123"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="D103:D106"/>
-    <mergeCell ref="E103:E106"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="D107:D110"/>
-    <mergeCell ref="E107:E110"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="E97:E99"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="D81:D87"/>
-    <mergeCell ref="E81:E87"/>
-    <mergeCell ref="A90:A96"/>
-    <mergeCell ref="B90:B96"/>
-    <mergeCell ref="D90:D96"/>
-    <mergeCell ref="E90:E96"/>
-    <mergeCell ref="D68:D77"/>
-    <mergeCell ref="E68:E77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="A59:A67"/>
-    <mergeCell ref="B59:B67"/>
-    <mergeCell ref="D59:D67"/>
-    <mergeCell ref="E59:E67"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="D10:D14"/>
+    <mergeCell ref="E10:E14"/>
+    <mergeCell ref="A195:A198"/>
+    <mergeCell ref="B195:B198"/>
+    <mergeCell ref="D195:D198"/>
+    <mergeCell ref="E195:E198"/>
+    <mergeCell ref="A199:A201"/>
+    <mergeCell ref="B199:B201"/>
+    <mergeCell ref="D199:D201"/>
+    <mergeCell ref="E199:E201"/>
+    <mergeCell ref="D29:D35"/>
+    <mergeCell ref="E29:E35"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="D38:D42"/>
+    <mergeCell ref="E38:E42"/>
+    <mergeCell ref="D16:D25"/>
+    <mergeCell ref="E16:E25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="D53:D58"/>
+    <mergeCell ref="E53:E58"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="B4:B8"/>
     <mergeCell ref="D4:D8"/>
@@ -14833,30 +14758,102 @@
     <mergeCell ref="B29:B35"/>
     <mergeCell ref="A16:A25"/>
     <mergeCell ref="B16:B25"/>
-    <mergeCell ref="D10:D14"/>
-    <mergeCell ref="E10:E14"/>
-    <mergeCell ref="A195:A198"/>
-    <mergeCell ref="B195:B198"/>
-    <mergeCell ref="D195:D198"/>
-    <mergeCell ref="E195:E198"/>
-    <mergeCell ref="A199:A201"/>
-    <mergeCell ref="B199:B201"/>
-    <mergeCell ref="D199:D201"/>
-    <mergeCell ref="E199:E201"/>
-    <mergeCell ref="D29:D35"/>
-    <mergeCell ref="E29:E35"/>
-    <mergeCell ref="A38:A42"/>
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="D38:D42"/>
-    <mergeCell ref="E38:E42"/>
-    <mergeCell ref="D16:D25"/>
-    <mergeCell ref="E16:E25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="D53:D58"/>
-    <mergeCell ref="E53:E58"/>
+    <mergeCell ref="A59:A67"/>
+    <mergeCell ref="B59:B67"/>
+    <mergeCell ref="D59:D67"/>
+    <mergeCell ref="E59:E67"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="D81:D87"/>
+    <mergeCell ref="E81:E87"/>
+    <mergeCell ref="A90:A96"/>
+    <mergeCell ref="B90:B96"/>
+    <mergeCell ref="D90:D96"/>
+    <mergeCell ref="E90:E96"/>
+    <mergeCell ref="D68:D77"/>
+    <mergeCell ref="E68:E77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="D103:D106"/>
+    <mergeCell ref="E103:E106"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="D107:D110"/>
+    <mergeCell ref="E107:E110"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="E97:E99"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="E101:E102"/>
+    <mergeCell ref="D125:D127"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="E132:E133"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="E111:E112"/>
+    <mergeCell ref="A115:A123"/>
+    <mergeCell ref="B115:B123"/>
+    <mergeCell ref="D115:D123"/>
+    <mergeCell ref="E115:E123"/>
+    <mergeCell ref="A145:A149"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="D145:D149"/>
+    <mergeCell ref="E145:E149"/>
+    <mergeCell ref="A151:A153"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="D151:D153"/>
+    <mergeCell ref="E151:E153"/>
+    <mergeCell ref="D139:D141"/>
+    <mergeCell ref="E139:E141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="A168:A170"/>
+    <mergeCell ref="B168:B170"/>
+    <mergeCell ref="D168:D170"/>
+    <mergeCell ref="E168:E170"/>
+    <mergeCell ref="A171:A175"/>
+    <mergeCell ref="B171:B175"/>
+    <mergeCell ref="D171:D175"/>
+    <mergeCell ref="E171:E175"/>
+    <mergeCell ref="A154:A161"/>
+    <mergeCell ref="B154:B161"/>
+    <mergeCell ref="D154:D161"/>
+    <mergeCell ref="E154:E161"/>
+    <mergeCell ref="A163:A165"/>
+    <mergeCell ref="B163:B165"/>
+    <mergeCell ref="D163:D165"/>
+    <mergeCell ref="E163:E165"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="D182:D183"/>
+    <mergeCell ref="E182:E183"/>
+    <mergeCell ref="A185:A191"/>
+    <mergeCell ref="B185:B191"/>
+    <mergeCell ref="D185:D191"/>
+    <mergeCell ref="E185:E191"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="E176:E177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="E178:E181"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16076,7 +16073,7 @@
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="2" t="s">
         <v>1260</v>
       </c>
       <c r="D95" s="4"/>
@@ -16514,78 +16511,6 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="A11:A19"/>
-    <mergeCell ref="B11:B19"/>
-    <mergeCell ref="D11:D19"/>
-    <mergeCell ref="E11:E19"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="D51:D55"/>
-    <mergeCell ref="E51:E55"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="D57:D61"/>
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="D70:D72"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="A74:A79"/>
-    <mergeCell ref="B74:B79"/>
-    <mergeCell ref="D74:D79"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="A84:A95"/>
-    <mergeCell ref="B84:B95"/>
-    <mergeCell ref="D84:D95"/>
-    <mergeCell ref="E84:E95"/>
-    <mergeCell ref="A96:A99"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="D96:D99"/>
-    <mergeCell ref="E96:E99"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="E103:E104"/>
     <mergeCell ref="A124:A131"/>
     <mergeCell ref="B124:B131"/>
     <mergeCell ref="D124:D131"/>
@@ -16598,6 +16523,78 @@
     <mergeCell ref="B122:B123"/>
     <mergeCell ref="D122:D123"/>
     <mergeCell ref="E122:E123"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="E101:E102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="E103:E104"/>
+    <mergeCell ref="A84:A95"/>
+    <mergeCell ref="B84:B95"/>
+    <mergeCell ref="D84:D95"/>
+    <mergeCell ref="E84:E95"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="E96:E99"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="D70:D72"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="A74:A79"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="D74:D79"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="D51:D55"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="B11:B19"/>
+    <mergeCell ref="D11:D19"/>
+    <mergeCell ref="E11:E19"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
